--- a/Planilha sem título.xlsx
+++ b/Planilha sem título.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dsv-git\Projeto Js\professor de teste\calculadora-pro-professor-\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1735868-A8C2-4383-A122-12E475DE3B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
+    <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
   <si>
     <t xml:space="preserve">RELATORIO DE FALHAS </t>
   </si>
@@ -164,42 +173,140 @@
   </si>
   <si>
     <t xml:space="preserve">input do cpf aceita qualquer coisa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sistema avisando q funciona </t>
+  </si>
+  <si>
+    <t>bug-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fica toda hora avisando que o sistema avisando desnecessariamente </t>
+  </si>
+  <si>
+    <t>apenas numeros e já configura para cpf na forma</t>
+  </si>
+  <si>
+    <t>colocar na hora de codar apenas number sem ser string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apenas avisar quando o sistema parar de funcionar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">colocar um limite de tempo maior ou apenas quando o sistema falhar mesmo </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">as cores visivelmente feia </t>
+  </si>
+  <si>
+    <t>bug-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as cores piscando loucamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> senac smo </t>
+  </si>
+  <si>
+    <t>cores visualmente agradaveis para o cliente</t>
+  </si>
+  <si>
+    <t>colocar cores visualmente bonitas para o visualisador</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>media</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00FF00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFFFF00"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF00FF00"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00FF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -208,7 +315,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -224,87 +331,96 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFF3F3F3"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFF3F3F3"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFF3F3F3"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00FF00"/>
+      <color rgb="FF1C5A2C"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -494,328 +610,507 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.88"/>
-    <col customWidth="1" min="2" max="10" width="17.88"/>
-    <col customWidth="1" min="13" max="13" width="6.0"/>
-    <col customWidth="1" min="14" max="14" width="38.88"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="10" width="17.85546875" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="10"/>
+      <c r="M2" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>46148.884722222225</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="10"/>
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="J5" s="10"/>
+      <c r="K5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="L5" s="10"/>
+      <c r="M5" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>46148.88958333333</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="10"/>
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="L6" s="10"/>
+      <c r="M6" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5">
-        <v>46148.89097222222</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="3">
+        <v>46148.890972222223</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="L7" s="10"/>
+      <c r="M7" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5">
-        <v>46148.89513888889</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="3">
+        <v>46148.895138888889</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="15"/>
+      <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="J8" s="10"/>
+      <c r="K8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="14">
-        <v>46148.89791666667</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="7">
+        <v>46148.897916666669</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="10"/>
+      <c r="G9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46148.900694444441</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46148.902777777781</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="19"/>
+      <c r="M11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="16">
+        <v>46154.849305555559</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="I12" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="5">
-        <v>46148.90069444444</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="L12" s="20"/>
+      <c r="M12" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="22"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46154.894444444442</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="E13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="K13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="5">
-        <v>46148.90277777778</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="G12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14">
-      <c r="G14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15">
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16">
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17">
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18">
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19">
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20">
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21">
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22">
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23">
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24">
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25">
-      <c r="H25" s="15"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="N13" s="23"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="G14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H25" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="44">
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:J4"/>
     <mergeCell ref="K2:L4"/>
@@ -825,32 +1120,8 @@
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="E2:F4"/>
     <mergeCell ref="G2:G4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>